--- a/report_forms/039_smart_water_usage_report_request_form--report_forms.xlsx
+++ b/report_forms/039_smart_water_usage_report_request_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,8 +788,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -817,12 +817,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'january_1_to_january_31'}</t>
+          <t>january_1_to_january_31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'January 1 to January 31'}</t>
+          <t>January 1 to January 31</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'february_1_to_february_28'}</t>
+          <t>february_1_to_february_28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'February 1 to February 28'}</t>
+          <t>February 1 to February 28</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'march_1_to_march_31'}</t>
+          <t>march_1_to_march_31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'March 1 to March 31'}</t>
+          <t>March 1 to March 31</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'april_1_to_april_31'}</t>
+          <t>april_1_to_april_31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'April 1 to April 31'}</t>
+          <t>April 1 to April 31</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'homeowner'}</t>
+          <t>homeowner</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Homeowner'}</t>
+          <t>Homeowner</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'landlord'}</t>
+          <t>landlord</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Landlord'}</t>
+          <t>Landlord</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'utility_representative'}</t>
+          <t>utility_representative</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Utility Representative'}</t>
+          <t>Utility Representative</t>
         </is>
       </c>
     </row>
